--- a/data/trans_orig/IP1011-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Provincia-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98248</t>
+          <t>97982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105419</t>
+          <t>105422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205730</t>
+          <t>205689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154878</t>
+          <t>154560</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159937</t>
+          <t>159524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316894</t>
+          <t>316689</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321962</t>
+          <t>321362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>677099</t>
+          <t>675887</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717450</t>
+          <t>717388</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396659</t>
+          <t>1396170</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402448</t>
+          <t>1402511</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101020</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212566</t>
+          <t>212830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67919</t>
+          <t>67459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135479</t>
+          <t>134545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112014</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142401</t>
+          <t>142244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281439</t>
+          <t>280718</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701965</t>
+          <t>702115</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>743501</t>
+          <t>743100</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448261</t>
+          <t>1448131</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454396</t>
+          <t>1454409</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167272</t>
+          <t>166740</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331826</t>
+          <t>332143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>741281</t>
+          <t>741966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1445116</t>
+          <t>1445301</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1011-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3580</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108090</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105431</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100901</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97982</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98250</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108090</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105422</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>318</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205689</t>
+          <t>206294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2893,47 +2893,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4534</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>162755</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>160065</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157299</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154560</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>155439</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>162755</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>159524</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>491</t>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316689</t>
+          <t>316634</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321362</t>
+          <t>321361</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5312</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>720730</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>716851</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722099</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679755</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>675887</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>676635</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>720730</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>717388</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722098</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396170</t>
+          <t>1396010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402511</t>
+          <t>1402455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4158,47 +4158,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4388,107 +4388,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4501,74 +4501,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104057</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101442</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>101425</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>316</t>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212830</t>
+          <t>212581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4731,107 +4731,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>651</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4217</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4844,72 +4844,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69933</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66640</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69933</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67459</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134545</t>
+          <t>135472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5873,74 +5873,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55229</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>52882</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>51748</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,65%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>161</t>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112385</t>
+          <t>112439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,107 +6103,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3495</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3739</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -6216,72 +6216,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145067</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>142384</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145067</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>142244</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280718</t>
+          <t>280970</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6559,47 +6559,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6794,67 +6794,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4606</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5042</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>746819</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>743536</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>705516</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>702115</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>702559</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>746819</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>743100</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448131</t>
+          <t>1448287</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454409</t>
+          <t>1454397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,107 +9769,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4109</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -9882,72 +9882,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170136</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167502</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170136</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>166740</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332143</t>
+          <t>331453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,107 +10112,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -10225,72 +10225,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>740906</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>741966</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1445301</t>
+          <t>1445662</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
